--- a/templates/Macro_model.xlsx
+++ b/templates/Macro_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n.barla\Documents\Local_codes\HVDCWISE_TEA.jl\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D8339-A4FA-45F8-9AB6-A7A2C37F991F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A4F72A-24D3-4488-9C9C-4096C5CA3887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C57834E6-C588-4116-B15D-7ADB3B8705E5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{C57834E6-C588-4116-B15D-7ADB3B8705E5}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="128">
   <si>
     <t>Content</t>
   </si>
@@ -436,6 +436,21 @@
   </si>
   <si>
     <t>Number of real lines in parallel. 1 if not a reduced edge</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>°</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>North coordinate</t>
+  </si>
+  <si>
+    <t>East coordinate</t>
   </si>
 </sst>
 </file>
@@ -1310,13 +1325,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18BB911-CA77-4F8E-9EB2-20225661F621}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1326,8 +1341,14 @@
       <c r="C1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1337,8 +1358,14 @@
       <c r="C2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1348,8 +1375,14 @@
       <c r="C3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -1359,8 +1392,14 @@
       <c r="C4">
         <v>400</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>45</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1369,6 +1408,12 @@
       </c>
       <c r="C5">
         <v>400</v>
+      </c>
+      <c r="D5">
+        <v>46</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1378,13 +1423,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E426320-1014-411C-AA19-D0D57F06F18F}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1394,8 +1439,14 @@
       <c r="C1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1405,8 +1456,14 @@
       <c r="C2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1416,8 +1473,14 @@
       <c r="C3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -1427,8 +1490,14 @@
       <c r="C4">
         <v>320</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>45</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -1437,6 +1506,12 @@
       </c>
       <c r="C5">
         <v>320</v>
+      </c>
+      <c r="D5">
+        <v>46</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2158,6 +2233,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_Flow_SignoffStatus xmlns="37bcdbbe-1b84-46f8-a2e4-bedf5bd24576" xsi:nil="true"/>
@@ -2169,7 +2253,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100360305CF8A5F8A4B86568FB88F41EB51" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7820bdd98b12bbce6701f392baa49827">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="37bcdbbe-1b84-46f8-a2e4-bedf5bd24576" xmlns:ns3="e2fe3da4-e7b1-4e71-a513-56b717f56f6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a7208ee71179b2cd86960a83168177e" ns2:_="" ns3:_="">
     <xsd:import namespace="37bcdbbe-1b84-46f8-a2e4-bedf5bd24576"/>
@@ -2410,16 +2494,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7ED9F52-07AC-4C0A-AC76-FFC7BB308E31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DAE2862-7911-45BF-8962-6BF015BBFC66}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2430,7 +2513,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51054561-08D6-4033-8FFD-879157D5F173}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2447,12 +2530,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7ED9F52-07AC-4C0A-AC76-FFC7BB308E31}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>